--- a/gas_net/kai_inf_horizon_60hrs.xlsx
+++ b/gas_net/kai_inf_horizon_60hrs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssnaik\Biegler\gas_networks_italy\gas_networks\gas_net\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13259D28-DC40-4957-9BCB-4B1FDECBAD01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD20056A-3752-4BA5-AA5C-07176480BFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30720" yWindow="1920" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="compressor power" sheetId="1" r:id="rId1"/>
@@ -533,10 +533,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,7 +547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -561,7 +561,7 @@
         <v>1.632137333748309E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -575,7 +575,7 @@
         <v>2.289101656244464E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -589,7 +589,7 @@
         <v>4.9185463431298537E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -603,7 +603,7 @@
         <v>6.4384159954459785E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -616,12 +616,8 @@
       <c r="D6">
         <v>5.193645567720051E-2</v>
       </c>
-      <c r="F6">
-        <f>SUM(B2:D26)</f>
-        <v>4.9988866139889634</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -635,7 +631,7 @@
         <v>5.3219043561801523E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -649,7 +645,7 @@
         <v>6.5730111182076403E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -663,7 +659,7 @@
         <v>7.7537345174050532E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -677,7 +673,7 @@
         <v>7.6176564673247224E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -691,7 +687,7 @@
         <v>6.3141982128695068E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -705,7 +701,7 @@
         <v>6.1685454495233688E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -719,7 +715,7 @@
         <v>6.3616311364603148E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -733,7 +729,7 @@
         <v>7.8680538048865448E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -747,7 +743,7 @@
         <v>9.2938441194441501E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
